--- a/terminology/ECG_terminology_crosswalk.xlsx
+++ b/terminology/ECG_terminology_crosswalk.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="843">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">余心电图正常</t>
   </si>
   <si>
-    <t xml:space="preserve">大致正常心电图（×14：专家4 ×14、专家5 ×0）；除心率外心电图正常（×2：专家4 ×2、专家5 ×0）；心电图大致正常（×2：专家4 ×0、专家5 ×2）</t>
+    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">大致正常心电图（×7）；除心率减慢外（×7）；除心率增快外（×5）；余心电图正常（×2）；心电图大致正常（×2）；除心率外心电图正常（×2）</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">异常心电图</t>
   </si>
   <si>
-    <t xml:space="preserve">提示心肌缺血可能异常心电图（×1：专家4 ×1、专家5 ×0）；时期未定异常心电图（×1：专家4 ×0、专家5 ×1）；心电图异常（×4）：原始写法 『心电图异常。』×3、『心电图异常』×1</t>
+    <t xml:space="preserve">提示心肌缺血可能异常心电图（×1：专家4 ×1、专家5 ×0）；时期未定异常心电图（×1：专家4 ×0、专家5 ×1）</t>
   </si>
   <si>
     <t xml:space="preserve">异常心电图（×32）；心电图异常（×4）；时期未定异常心电图（×1）；提示心肌缺血可能异常心电图（×1）</t>
@@ -142,15 +142,15 @@
     <t xml:space="preserve">abnormal ecg（×355656）；summary: abnormal ecg（×3648）</t>
   </si>
   <si>
+    <t xml:space="preserve">心电图异常（×4）：原始写法 『心电图异常。』×3、『心电图异常』×1</t>
+  </si>
+  <si>
     <t xml:space="preserve">uninterpretable ECG</t>
   </si>
   <si>
     <t xml:space="preserve">无法判读的心电图</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical conditions</t>
   </si>
   <si>
@@ -1054,24 +1054,24 @@
     <t xml:space="preserve">不完全性右束支阻滞</t>
   </si>
   <si>
+    <t xml:space="preserve">不完全性右束支传导阻滞（×24）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不完全性右束支传导阻滞（×91）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不完全性右束支传导阻滞（×22）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incomplete right bundle branch block（×1106）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incomplete right bundle branch block（×1118）</t>
+  </si>
+  <si>
     <t xml:space="preserve">不完全性右束支传导阻滞（×137）：原始写法 『不完全性右束支传导阻滞』×136、『不完全性右束支传导阻滞。』×1</t>
   </si>
   <si>
-    <t xml:space="preserve">不完全性右束支传导阻滞（×24）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不完全性右束支传导阻滞（×91）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不完全性右束支传导阻滞（×22）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incomplete right bundle branch block（×1106）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incomplete right bundle branch block（×1118）</t>
-  </si>
-  <si>
     <t xml:space="preserve">right bundle-branch block</t>
   </si>
   <si>
@@ -2185,6 +2185,9 @@
     <t xml:space="preserve">提示：P 列在 #41 室性期前收缩（391 项）、#106 前壁心肌梗死（343 项）、#61 一度房室阻滞（250 项）等高频行仍混有与本术语无关的机器写法，系匹配规则过宽所致，需按行重建规则后复核，未在本次逐项改动。</t>
   </si>
   <si>
+    <t xml:space="preserve">【v6 列修正说明（2026-09-20）】经专家复核，K 列『专家使用术语形式』存在两类问题已校正：① #2 余心电图正常 中『大致正常心电图 / 除心率外心电图正常 / 心电图大致正常』专家确认评审中未使用，K 清空；② #3、#73 两行 K 列混入了『原始写法』库侧词形归并文本（本应只在 R 列），已迁出至 R 列。K 列现仅保留经专家署名确认的实际写法。</t>
+  </si>
+  <si>
     <t xml:space="preserve">v2 修正日志(基于 2026-09-15 第三方 OCR 像素级复核报告)</t>
   </si>
   <si>
@@ -2513,6 +2516,36 @@
   </si>
   <si>
     <t xml:space="preserve">口径不变式（v4 起生效，v5 扩至全量列）：同一句原始写法在 K/M/N/O 合并后只能对应一个标准词；P/Q（全量库参考列）亦不得跨行重复。v5 共纠正 126 处。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v6 列修正日志（2026-09-20 K 列专家署名 / 库侧文本串列复核）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2 余心电图正常 K 列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大致正常心电图（×14：专家4 ×14）；除心率外心电图正常（×2：专家4 ×2）；心电图大致正常（×2：专家5 ×2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清空（专家复核确认评审中未使用这些词；J 由『是』改『—』）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3 异常心电图 K 列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">含『心电图异常（×4）：原始写法 『心电图异常。』×3、『心电图异常』×1』库侧文本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库侧文本迁出至 R 列；K 仅保留 2 条专家实际写法</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#73 不完全性右束支阻滞 K 列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">整段为库侧归并文本『不完全性右束支传导阻滞（×137）：原始写法 …』</t>
+  </si>
+  <si>
+    <t xml:space="preserve">整段迁至 R 列；K 清空（J 由『是』改『—』）</t>
   </si>
 </sst>
 </file>
@@ -4033,9 +4066,6 @@
         <v>1</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="0" t="s">
         <v>32</v>
       </c>
       <c r="L3" s="34" t="s">
@@ -4088,16 +4118,19 @@
       <c r="P4" s="36" t="s">
         <v>40</v>
       </c>
+      <c r="R4" s="0" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="5" outlineLevel="1" ht="22" customFormat="1" customHeight="1" s="34">
       <c r="A5" s="37" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="34" t="s">
         <v>22</v>
@@ -4112,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L5" s="34" t="s">
         <v>25</v>
@@ -4220,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L8" s="34" t="s">
         <v>25</v>
@@ -4249,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L9" s="34" t="s">
         <v>25</v>
@@ -4278,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L10" s="34" t="s">
         <v>25</v>
@@ -4310,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L11" s="34" t="s">
         <v>25</v>
@@ -4345,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L12" s="34" t="s">
         <v>25</v>
@@ -4626,12 +4659,12 @@
         <v>0</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L19" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="0" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4658,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L20" s="34" t="s">
         <v>25</v>
@@ -4690,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L21" s="34" t="s">
         <v>25</v>
@@ -4807,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L24" s="34" t="s">
         <v>25</v>
@@ -4836,12 +4869,12 @@
         <v>0</v>
       </c>
       <c r="J25" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L25" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25" s="0" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4897,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L27" s="34" t="s">
         <v>25</v>
@@ -5125,12 +5158,12 @@
         <v>0</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L33" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P33" s="0" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5157,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L34" s="34" t="s">
         <v>25</v>
@@ -5333,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L38" s="34" t="s">
         <v>25</v>
@@ -5362,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L39" s="34" t="s">
         <v>25</v>
@@ -5432,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L41" s="34" t="s">
         <v>25</v>
@@ -5514,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L43" s="34" t="s">
         <v>25</v>
@@ -5546,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L44" s="34" t="s">
         <v>25</v>
@@ -5575,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L45" s="34" t="s">
         <v>25</v>
@@ -5642,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L47" s="34" t="s">
         <v>25</v>
@@ -5671,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L48" s="34" t="s">
         <v>25</v>
@@ -5700,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L49" s="34" t="s">
         <v>25</v>
@@ -5729,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L50" s="34" t="s">
         <v>25</v>
@@ -5764,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L51" s="34" t="s">
         <v>25</v>
@@ -5796,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L52" s="34" t="s">
         <v>25</v>
@@ -5825,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L53" s="34" t="s">
         <v>25</v>
@@ -5854,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L54" s="34" t="s">
         <v>25</v>
@@ -5883,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L55" s="34" t="s">
         <v>25</v>
@@ -5912,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L56" s="34" t="s">
         <v>25</v>
@@ -5941,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L57" s="34" t="s">
         <v>25</v>
@@ -5970,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L58" s="34" t="s">
         <v>25</v>
@@ -6049,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L60" s="34" t="s">
         <v>25</v>
@@ -6216,12 +6249,12 @@
         <v>0</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L64" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P64" t="s">
+      <c r="P64" s="0" t="s">
         <v>292</v>
       </c>
     </row>
@@ -6289,12 +6322,12 @@
         <v>0</v>
       </c>
       <c r="J66" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L66" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P66" t="s">
+      <c r="P66" s="0" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6321,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L67" s="34" t="s">
         <v>25</v>
@@ -6394,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L69" s="34" t="s">
         <v>25</v>
@@ -6608,27 +6641,27 @@
         <v>1</v>
       </c>
       <c r="J74" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="L74" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M74" s="36" t="s">
+      <c r="N74" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="N74" s="36" t="s">
+      <c r="O74" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="O74" s="36" t="s">
+      <c r="P74" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="P74" s="36" t="s">
+      <c r="Q74" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="Q74" s="36" t="s">
+      <c r="R74" s="0" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6790,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L78" s="34" t="s">
         <v>25</v>
@@ -6819,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L79" s="34" t="s">
         <v>25</v>
@@ -6848,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L80" s="34" t="s">
         <v>25</v>
@@ -6971,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L83" s="34" t="s">
         <v>25</v>
@@ -7003,12 +7036,12 @@
         <v>0</v>
       </c>
       <c r="J84" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L84" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84" s="0" t="s">
         <v>400</v>
       </c>
     </row>
@@ -7035,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L85" s="34" t="s">
         <v>25</v>
@@ -7125,7 +7158,7 @@
       <c r="O87" s="0" t="s">
         <v>415</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P87" s="0" t="s">
         <v>416</v>
       </c>
     </row>
@@ -7237,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L90" s="34" t="s">
         <v>25</v>
@@ -7451,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L95" s="34" t="s">
         <v>25</v>
@@ -7671,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L100" s="34" t="s">
         <v>25</v>
@@ -7738,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L102" s="34" t="s">
         <v>25</v>
@@ -7767,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L103" s="34" t="s">
         <v>25</v>
@@ -7796,12 +7829,12 @@
         <v>0</v>
       </c>
       <c r="J104" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L104" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P104" t="s">
+      <c r="P104" s="0" t="s">
         <v>510</v>
       </c>
     </row>
@@ -7828,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L105" s="34" t="s">
         <v>25</v>
@@ -7980,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L109" s="34" t="s">
         <v>25</v>
@@ -8012,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L110" s="34" t="s">
         <v>25</v>
@@ -8085,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L112" s="34" t="s">
         <v>25</v>
@@ -8117,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L113" s="34" t="s">
         <v>25</v>
@@ -8146,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L114" s="34" t="s">
         <v>25</v>
@@ -8310,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L118" s="34" t="s">
         <v>25</v>
@@ -8339,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L119" s="34" t="s">
         <v>25</v>
@@ -8406,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L121" s="34" t="s">
         <v>25</v>
@@ -8435,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L122" s="34" t="s">
         <v>25</v>
@@ -8467,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L123" s="34" t="s">
         <v>25</v>
@@ -8496,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L124" s="34" t="s">
         <v>25</v>
@@ -8525,12 +8558,12 @@
         <v>0</v>
       </c>
       <c r="J125" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L125" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P125" t="s">
+      <c r="P125" s="0" t="s">
         <v>592</v>
       </c>
     </row>
@@ -8557,18 +8590,18 @@
         <v>0</v>
       </c>
       <c r="J126" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L126" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="P126" t="s">
+      <c r="P126" s="0" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C127" s="34" t="s">
         <v>433</v>
@@ -8592,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L127" s="34" t="s">
         <v>599</v>
@@ -8603,7 +8636,7 @@
     </row>
     <row r="128">
       <c r="A128" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C128" s="34" t="s">
         <v>19</v>
@@ -8627,7 +8660,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L128" s="34" t="s">
         <v>599</v>
@@ -8644,7 +8677,7 @@
     </row>
     <row r="129">
       <c r="A129" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C129" s="34" t="s">
         <v>558</v>
@@ -8688,7 +8721,7 @@
       <c r="P129" s="36" t="s">
         <v>612</v>
       </c>
-      <c r="Q129" t="s">
+      <c r="Q129" s="0" t="s">
         <v>613</v>
       </c>
       <c r="R129" s="34" t="s">
@@ -8697,7 +8730,7 @@
     </row>
     <row r="130">
       <c r="A130" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C130" s="34" t="s">
         <v>171</v>
@@ -8721,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L130" s="34" t="s">
         <v>599</v>
@@ -8735,7 +8768,7 @@
     </row>
     <row r="131">
       <c r="A131" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C131" s="34" t="s">
         <v>116</v>
@@ -8759,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L131" s="34" t="s">
         <v>599</v>
@@ -8773,7 +8806,7 @@
     </row>
     <row r="132">
       <c r="A132" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C132" s="34" t="s">
         <v>433</v>
@@ -8797,7 +8830,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L132" s="34" t="s">
         <v>599</v>
@@ -8814,7 +8847,7 @@
     </row>
     <row r="133">
       <c r="A133" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C133" s="34" t="s">
         <v>433</v>
@@ -8838,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L133" s="34" t="s">
         <v>599</v>
@@ -8858,7 +8891,7 @@
     </row>
     <row r="134">
       <c r="A134" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C134" s="34" t="s">
         <v>380</v>
@@ -8882,7 +8915,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="34" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L134" s="34" t="s">
         <v>599</v>
@@ -8923,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="36" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L135" s="36" t="s">
         <v>643</v>
@@ -8964,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="36" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L136" s="36" t="s">
         <v>643</v>
@@ -9002,7 +9035,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="36" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L137" s="36" t="s">
         <v>643</v>
@@ -9040,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="36" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L138" s="36" t="s">
         <v>643</v>
@@ -9058,8 +9091,8 @@
     <mergeCell ref="B13:B21"/>
     <mergeCell ref="C91:C95"/>
     <mergeCell ref="B107:B115"/>
+    <mergeCell ref="B6:B12"/>
     <mergeCell ref="C59:C69"/>
-    <mergeCell ref="B6:B12"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C22:C34"/>
     <mergeCell ref="B116:B126"/>
@@ -9359,7 +9392,7 @@
         <v>674</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>125</v>
@@ -9379,7 +9412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22" customWidth="1" style="34" min="1" max="1"/>
@@ -9574,18 +9607,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" s="0" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" s="0" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" s="0" t="s">
         <v>721</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -9602,7 +9640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="6" customWidth="1" style="34" min="1" max="1"/>
@@ -9613,7 +9651,7 @@
   <sheetData>
     <row r="1" ht="28" customFormat="1" customHeight="1" s="34">
       <c r="A1" s="48" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" ht="26" customFormat="1" customHeight="1" s="34">
@@ -9621,24 +9659,24 @@
         <v>0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3" ht="32" customFormat="1" customHeight="1" s="34">
       <c r="A3" s="49" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D3" s="52" t="s">
         <v>433</v>
@@ -9646,13 +9684,13 @@
     </row>
     <row r="4" ht="32" customFormat="1" customHeight="1" s="34">
       <c r="A4" s="53" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D4" s="56" t="s">
         <v>512</v>
@@ -9660,13 +9698,13 @@
     </row>
     <row r="5" ht="32" customFormat="1" customHeight="1" s="34">
       <c r="A5" s="49" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D5" s="52" t="s">
         <v>514</v>
@@ -9674,64 +9712,64 @@
     </row>
     <row r="6" ht="32" customFormat="1" customHeight="1" s="34">
       <c r="A6" s="53" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8" ht="24" customFormat="1" customHeight="1" s="34">
       <c r="B8" s="57" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" ht="24" customFormat="1" customHeight="1" s="34">
       <c r="B9" s="58" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="10" ht="17" customFormat="1" customHeight="1" s="34">
       <c r="B10" s="59" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C10" s="60" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D10" s="61" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" ht="34" customFormat="1" customHeight="1" s="34">
       <c r="B11" s="59" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D11" s="61" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="62" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16">
@@ -9739,13 +9777,13 @@
         <v>0</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="17">
@@ -9753,13 +9791,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18">
@@ -9767,13 +9805,13 @@
         <v>2</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="19">
@@ -9781,13 +9819,13 @@
         <v>3</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="20">
@@ -9795,18 +9833,18 @@
         <v>4</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22">
@@ -9814,13 +9852,13 @@
         <v>0</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="23">
@@ -9828,13 +9866,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="24">
@@ -9842,18 +9880,18 @@
         <v>6</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="34" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27">
@@ -9861,252 +9899,313 @@
         <v>0</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="36" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="36" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="36" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="36" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="36" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="36" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="36" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="36" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="36" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
-        <v>807</v>
+      <c r="A40" s="0" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" t="s">
-        <v>723</v>
-      </c>
-      <c r="C41" t="s">
-        <v>751</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="A41" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="C41" s="0" t="s">
         <v>752</v>
       </c>
+      <c r="D41" s="0" t="s">
+        <v>753</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
-        <v>808</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42" s="0" t="s">
         <v>810</v>
       </c>
-      <c r="D42" t="s">
+      <c r="C42" s="0" t="s">
         <v>811</v>
       </c>
+      <c r="D42" s="0" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
-        <v>812</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="0" t="s">
         <v>813</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43" s="0" t="s">
         <v>814</v>
       </c>
-      <c r="D43" t="s">
+      <c r="C43" s="0" t="s">
         <v>815</v>
       </c>
+      <c r="D43" s="0" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>816</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="0" t="s">
         <v>817</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44" s="0" t="s">
         <v>818</v>
       </c>
-      <c r="D44" t="s">
+      <c r="C44" s="0" t="s">
         <v>819</v>
       </c>
+      <c r="D44" s="0" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>820</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="0" t="s">
         <v>821</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45" s="0" t="s">
         <v>822</v>
       </c>
-      <c r="D45" t="s">
+      <c r="C45" s="0" t="s">
         <v>823</v>
       </c>
+      <c r="D45" s="0" t="s">
+        <v>824</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
-        <v>824</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46" s="0" t="s">
+        <v>826</v>
+      </c>
+      <c r="C46" s="0" t="s">
         <v>613</v>
       </c>
-      <c r="D46" t="s">
-        <v>826</v>
+      <c r="D46" s="0" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>827</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="0" t="s">
         <v>828</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47" s="0" t="s">
         <v>829</v>
       </c>
-      <c r="D47" t="s">
+      <c r="C47" s="0" t="s">
         <v>830</v>
       </c>
+      <c r="D47" s="0" t="s">
+        <v>831</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>831</v>
+      <c r="A48" s="0" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>724</v>
+      </c>
+      <c r="C51" t="s">
+        <v>752</v>
+      </c>
+      <c r="D51" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>834</v>
+      </c>
+      <c r="C52" t="s">
+        <v>835</v>
+      </c>
+      <c r="D52" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>837</v>
+      </c>
+      <c r="C53" t="s">
+        <v>838</v>
+      </c>
+      <c r="D53" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>840</v>
+      </c>
+      <c r="C54" t="s">
+        <v>841</v>
+      </c>
+      <c r="D54" t="s">
+        <v>842</v>
       </c>
     </row>
   </sheetData>
